--- a/reports_sample/แบบฟอร์มทะเบียนครุภัณฑ์_ตัวอย่าง.xlsx
+++ b/reports_sample/แบบฟอร์มทะเบียนครุภัณฑ์_ตัวอย่าง.xlsx
@@ -421,7 +421,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ส่วนราชการ: คณะพยาบาลศาสตร์       หน่วยงานผู้ครอบครอง: ศูนย์ฝึกทักษะการพยาบาล (Nursing Lab)       ประเภท: ครุภัณฑ์การแพทย์และฝึกทักษะ</v>
+        <v>ส่วนราชการ: คณะพยาบาลศาสตร์ มหาวิทยาลัยเกษตรศาสตร์       หน่วยงานผู้ครอบครอง: ศูนย์การเรียนรู้ปฏิบัติการทางการพยาบาลเสมือนจริง       ประเภท: ครุภัณฑ์การแพทย์และฝึกทักษะ</v>
       </c>
     </row>
     <row r="3">
@@ -505,7 +505,7 @@
         <v>พร้อมใช้งาน</v>
       </c>
       <c r="L6" t="str">
-        <v>ศูนย์ฝึกทักษะการพยาบาล คณะพยาบาลศาสตร์</v>
+        <v>ศูนย์การเรียนรู้ปฏิบัติการทางการพยาบาลเสมือนจริง คณะพยาบาลศาสตร์</v>
       </c>
       <c r="M6" t="str">
         <v>-</v>
@@ -546,7 +546,7 @@
         <v>พร้อมใช้งาน</v>
       </c>
       <c r="L7" t="str">
-        <v>ศูนย์ฝึกทักษะการพยาบาล คณะพยาบาลศาสตร์</v>
+        <v>ศูนย์การเรียนรู้ปฏิบัติการทางการพยาบาลเสมือนจริง คณะพยาบาลศาสตร์</v>
       </c>
       <c r="M7" t="str">
         <v>-</v>
@@ -587,7 +587,7 @@
         <v>พร้อมใช้งาน</v>
       </c>
       <c r="L8" t="str">
-        <v>ศูนย์ฝึกทักษะการพยาบาล คณะพยาบาลศาสตร์</v>
+        <v>ศูนย์การเรียนรู้ปฏิบัติการทางการพยาบาลเสมือนจริง คณะพยาบาลศาสตร์</v>
       </c>
       <c r="M8" t="str">
         <v>-</v>
@@ -628,7 +628,7 @@
         <v>พร้อมใช้งาน</v>
       </c>
       <c r="L9" t="str">
-        <v>ศูนย์ฝึกทักษะการพยาบาล คณะพยาบาลศาสตร์</v>
+        <v>ศูนย์การเรียนรู้ปฏิบัติการทางการพยาบาลเสมือนจริง คณะพยาบาลศาสตร์</v>
       </c>
       <c r="M9" t="str">
         <v>-</v>
@@ -669,7 +669,7 @@
         <v>พร้อมใช้งาน</v>
       </c>
       <c r="L10" t="str">
-        <v>ศูนย์ฝึกทักษะการพยาบาล คณะพยาบาลศาสตร์</v>
+        <v>ศูนย์การเรียนรู้ปฏิบัติการทางการพยาบาลเสมือนจริง คณะพยาบาลศาสตร์</v>
       </c>
       <c r="M10" t="str">
         <v>-</v>
@@ -710,7 +710,7 @@
         <v>พร้อมใช้งาน</v>
       </c>
       <c r="L11" t="str">
-        <v>ศูนย์ฝึกทักษะการพยาบาล คณะพยาบาลศาสตร์</v>
+        <v>ศูนย์การเรียนรู้ปฏิบัติการทางการพยาบาลเสมือนจริง คณะพยาบาลศาสตร์</v>
       </c>
       <c r="M11" t="str">
         <v>-</v>
@@ -751,7 +751,7 @@
         <v>พร้อมใช้งาน</v>
       </c>
       <c r="L12" t="str">
-        <v>ศูนย์ฝึกทักษะการพยาบาล คณะพยาบาลศาสตร์</v>
+        <v>ศูนย์การเรียนรู้ปฏิบัติการทางการพยาบาลเสมือนจริง คณะพยาบาลศาสตร์</v>
       </c>
       <c r="M12" t="str">
         <v>-</v>
@@ -792,7 +792,7 @@
         <v>พร้อมใช้งาน</v>
       </c>
       <c r="L13" t="str">
-        <v>ศูนย์ฝึกทักษะการพยาบาล คณะพยาบาลศาสตร์</v>
+        <v>ศูนย์การเรียนรู้ปฏิบัติการทางการพยาบาลเสมือนจริง คณะพยาบาลศาสตร์</v>
       </c>
       <c r="M13" t="str">
         <v>-</v>
@@ -833,7 +833,7 @@
         <v>พร้อมใช้งาน</v>
       </c>
       <c r="L14" t="str">
-        <v>ศูนย์ฝึกทักษะการพยาบาล คณะพยาบาลศาสตร์</v>
+        <v>ศูนย์การเรียนรู้ปฏิบัติการทางการพยาบาลเสมือนจริง คณะพยาบาลศาสตร์</v>
       </c>
       <c r="M14" t="str">
         <v>-</v>
@@ -874,7 +874,7 @@
         <v>พร้อมใช้งาน</v>
       </c>
       <c r="L15" t="str">
-        <v>ศูนย์ฝึกทักษะการพยาบาล คณะพยาบาลศาสตร์</v>
+        <v>ศูนย์การเรียนรู้ปฏิบัติการทางการพยาบาลเสมือนจริง คณะพยาบาลศาสตร์</v>
       </c>
       <c r="M15" t="str">
         <v>-</v>
@@ -915,7 +915,7 @@
         <v>พร้อมใช้งาน</v>
       </c>
       <c r="L16" t="str">
-        <v>ศูนย์ฝึกทักษะการพยาบาล คณะพยาบาลศาสตร์</v>
+        <v>ศูนย์การเรียนรู้ปฏิบัติการทางการพยาบาลเสมือนจริง คณะพยาบาลศาสตร์</v>
       </c>
       <c r="M16" t="str">
         <v>-</v>
@@ -956,7 +956,7 @@
         <v>พร้อมใช้งาน</v>
       </c>
       <c r="L17" t="str">
-        <v>ศูนย์ฝึกทักษะการพยาบาล คณะพยาบาลศาสตร์</v>
+        <v>ศูนย์การเรียนรู้ปฏิบัติการทางการพยาบาลเสมือนจริง คณะพยาบาลศาสตร์</v>
       </c>
       <c r="M17" t="str">
         <v>-</v>
@@ -997,7 +997,7 @@
         <v>พร้อมใช้งาน</v>
       </c>
       <c r="L18" t="str">
-        <v>ศูนย์ฝึกทักษะการพยาบาล คณะพยาบาลศาสตร์</v>
+        <v>ศูนย์การเรียนรู้ปฏิบัติการทางการพยาบาลเสมือนจริง คณะพยาบาลศาสตร์</v>
       </c>
       <c r="M18" t="str">
         <v>-</v>
@@ -1038,7 +1038,7 @@
         <v>พร้อมใช้งาน</v>
       </c>
       <c r="L19" t="str">
-        <v>ศูนย์ฝึกทักษะการพยาบาล คณะพยาบาลศาสตร์</v>
+        <v>ศูนย์การเรียนรู้ปฏิบัติการทางการพยาบาลเสมือนจริง คณะพยาบาลศาสตร์</v>
       </c>
       <c r="M19" t="str">
         <v>-</v>
@@ -1079,7 +1079,7 @@
         <v>พร้อมใช้งาน</v>
       </c>
       <c r="L20" t="str">
-        <v>ศูนย์ฝึกทักษะการพยาบาล คณะพยาบาลศาสตร์</v>
+        <v>ศูนย์การเรียนรู้ปฏิบัติการทางการพยาบาลเสมือนจริง คณะพยาบาลศาสตร์</v>
       </c>
       <c r="M20" t="str">
         <v>-</v>
@@ -1120,7 +1120,7 @@
         <v>พร้อมใช้งาน</v>
       </c>
       <c r="L21" t="str">
-        <v>ศูนย์ฝึกทักษะการพยาบาล คณะพยาบาลศาสตร์</v>
+        <v>ศูนย์การเรียนรู้ปฏิบัติการทางการพยาบาลเสมือนจริง คณะพยาบาลศาสตร์</v>
       </c>
       <c r="M21" t="str">
         <v>-</v>
@@ -1161,7 +1161,7 @@
         <v>พร้อมใช้งาน</v>
       </c>
       <c r="L22" t="str">
-        <v>ศูนย์ฝึกทักษะการพยาบาล คณะพยาบาลศาสตร์</v>
+        <v>ศูนย์การเรียนรู้ปฏิบัติการทางการพยาบาลเสมือนจริง คณะพยาบาลศาสตร์</v>
       </c>
       <c r="M22" t="str">
         <v>-</v>
@@ -1202,7 +1202,7 @@
         <v>พร้อมใช้งาน</v>
       </c>
       <c r="L23" t="str">
-        <v>ศูนย์ฝึกทักษะการพยาบาล คณะพยาบาลศาสตร์</v>
+        <v>ศูนย์การเรียนรู้ปฏิบัติการทางการพยาบาลเสมือนจริง คณะพยาบาลศาสตร์</v>
       </c>
       <c r="M23" t="str">
         <v>-</v>
@@ -1243,7 +1243,7 @@
         <v>พร้อมใช้งาน</v>
       </c>
       <c r="L24" t="str">
-        <v>ศูนย์ฝึกทักษะการพยาบาล คณะพยาบาลศาสตร์</v>
+        <v>ศูนย์การเรียนรู้ปฏิบัติการทางการพยาบาลเสมือนจริง คณะพยาบาลศาสตร์</v>
       </c>
       <c r="M24" t="str">
         <v>-</v>
@@ -1284,7 +1284,7 @@
         <v>พร้อมใช้งาน</v>
       </c>
       <c r="L25" t="str">
-        <v>ศูนย์ฝึกทักษะการพยาบาล คณะพยาบาลศาสตร์</v>
+        <v>ศูนย์การเรียนรู้ปฏิบัติการทางการพยาบาลเสมือนจริง คณะพยาบาลศาสตร์</v>
       </c>
       <c r="M25" t="str">
         <v>-</v>
